--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488128_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488128_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>9.2501</v>
+        <v>8.219900000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>6.8122</v>
+        <v>6.1267</v>
       </c>
       <c r="F2" t="n">
-        <v>2.4379</v>
+        <v>2.0932</v>
       </c>
       <c r="G2" t="n">
         <v>1.3428</v>
@@ -610,13 +610,13 @@
         <v>1.6676</v>
       </c>
       <c r="S2" t="n">
-        <v>1.8332</v>
+        <v>0.803</v>
       </c>
       <c r="T2" t="n">
-        <v>0.8133</v>
+        <v>0.1278</v>
       </c>
       <c r="U2" t="n">
-        <v>1.0199</v>
+        <v>0.6752</v>
       </c>
       <c r="V2" t="n">
         <v>4.4065</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. MARTINEZ AGUDO</t>
+          <t>J. NDJUNGU</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.7428</v>
+        <v>6.8713</v>
       </c>
       <c r="E3" t="n">
-        <v>3.2739</v>
+        <v>4.4667</v>
       </c>
       <c r="F3" t="n">
-        <v>3.4689</v>
+        <v>2.4046</v>
       </c>
       <c r="G3" t="n">
-        <v>2.6087</v>
+        <v>3.3334</v>
       </c>
       <c r="H3" t="n">
-        <v>0.6349</v>
+        <v>2.2075</v>
       </c>
       <c r="I3" t="n">
-        <v>1.9738</v>
+        <v>1.1259</v>
       </c>
       <c r="J3" t="n">
-        <v>2.1931</v>
+        <v>4.8355</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1503</v>
+        <v>2.8342</v>
       </c>
       <c r="L3" t="n">
-        <v>2.0428</v>
+        <v>2.0013</v>
       </c>
       <c r="M3" t="n">
-        <v>0.4156</v>
+        <v>-1.5021</v>
       </c>
       <c r="N3" t="n">
-        <v>0.4846</v>
+        <v>-0.6267</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.06900000000000001</v>
+        <v>-0.8754</v>
       </c>
       <c r="P3" t="n">
-        <v>2.4087</v>
+        <v>0.9264</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-1.8529</v>
       </c>
       <c r="R3" t="n">
-        <v>2.4087</v>
+        <v>2.7793</v>
       </c>
       <c r="S3" t="n">
-        <v>0.4666</v>
+        <v>0.4082</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.4924</v>
+        <v>-0.0892</v>
       </c>
       <c r="U3" t="n">
-        <v>0.959</v>
+        <v>0.4974</v>
       </c>
       <c r="V3" t="n">
-        <v>1.2589</v>
+        <v>2.2033</v>
       </c>
       <c r="W3" t="n">
         <v>1.5733</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.3144</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. NDJUNGU</t>
+          <t>A. MARTINEZ AGUDO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>6.7006</v>
+        <v>6.815</v>
       </c>
       <c r="E4" t="n">
-        <v>4.1729</v>
+        <v>3.5677</v>
       </c>
       <c r="F4" t="n">
-        <v>2.5277</v>
+        <v>3.2473</v>
       </c>
       <c r="G4" t="n">
-        <v>3.3334</v>
+        <v>2.6087</v>
       </c>
       <c r="H4" t="n">
-        <v>2.2075</v>
+        <v>0.6349</v>
       </c>
       <c r="I4" t="n">
-        <v>1.1259</v>
+        <v>1.9738</v>
       </c>
       <c r="J4" t="n">
-        <v>4.8355</v>
+        <v>2.1931</v>
       </c>
       <c r="K4" t="n">
-        <v>2.8342</v>
+        <v>0.1503</v>
       </c>
       <c r="L4" t="n">
-        <v>2.0013</v>
+        <v>2.0428</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.5021</v>
+        <v>0.4156</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.6267</v>
+        <v>0.4846</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.8754</v>
+        <v>-0.06900000000000001</v>
       </c>
       <c r="P4" t="n">
-        <v>0.9264</v>
+        <v>2.4087</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.8529</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.7793</v>
+        <v>2.4087</v>
       </c>
       <c r="S4" t="n">
-        <v>0.2375</v>
+        <v>0.5387999999999999</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.383</v>
+        <v>-0.1986</v>
       </c>
       <c r="U4" t="n">
-        <v>0.6205000000000001</v>
+        <v>0.7374000000000001</v>
       </c>
       <c r="V4" t="n">
-        <v>2.2033</v>
+        <v>1.2589</v>
       </c>
       <c r="W4" t="n">
         <v>1.5733</v>
       </c>
       <c r="X4" t="n">
-        <v>0.63</v>
+        <v>-0.3144</v>
       </c>
     </row>
     <row r="5">
@@ -799,10 +799,10 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>5.1494</v>
+        <v>5.0515</v>
       </c>
       <c r="E5" t="n">
-        <v>1.341</v>
+        <v>1.2431</v>
       </c>
       <c r="F5" t="n">
         <v>3.8084</v>
@@ -844,10 +844,10 @@
         <v>2.7793</v>
       </c>
       <c r="S5" t="n">
-        <v>0.2524</v>
+        <v>0.1545</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.0584</v>
+        <v>-0.1564</v>
       </c>
       <c r="U5" t="n">
         <v>0.3109</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>3.3143</v>
+        <v>3.217</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9029</v>
+        <v>0.7071</v>
       </c>
       <c r="F6" t="n">
-        <v>2.4114</v>
+        <v>2.5099</v>
       </c>
       <c r="G6" t="n">
         <v>2.0064</v>
@@ -922,13 +922,13 @@
         <v>1.1117</v>
       </c>
       <c r="S6" t="n">
-        <v>0.1962</v>
+        <v>0.0989</v>
       </c>
       <c r="T6" t="n">
-        <v>0.3793</v>
+        <v>0.1834</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1831</v>
+        <v>-0.08459999999999999</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>3.0682</v>
+        <v>2.9709</v>
       </c>
       <c r="E7" t="n">
-        <v>1.9111</v>
+        <v>1.7153</v>
       </c>
       <c r="F7" t="n">
-        <v>1.1571</v>
+        <v>1.2556</v>
       </c>
       <c r="G7" t="n">
         <v>3.9672</v>
@@ -1000,13 +1000,13 @@
         <v>2.2234</v>
       </c>
       <c r="S7" t="n">
-        <v>0.2509</v>
+        <v>0.1536</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1604</v>
+        <v>-0.0354</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0905</v>
+        <v>0.189</v>
       </c>
       <c r="V7" t="n">
         <v>1.2589</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>2.6164</v>
+        <v>2.7384</v>
       </c>
       <c r="E8" t="n">
-        <v>1.5916</v>
+        <v>1.7875</v>
       </c>
       <c r="F8" t="n">
-        <v>1.0248</v>
+        <v>0.9509</v>
       </c>
       <c r="G8" t="n">
         <v>2.6932</v>
@@ -1078,13 +1078,13 @@
         <v>0.7411</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.1885</v>
+        <v>-0.0665</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1641</v>
+        <v>0.0317</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0244</v>
+        <v>-0.0982</v>
       </c>
       <c r="V8" t="n">
         <v>-0.6294</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. CANDELA SOLO DE ZALDIVAR</t>
+          <t>L. DALLACOSTA ORTIZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1.952</v>
+        <v>2.3844</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.4172</v>
+        <v>2.0379</v>
       </c>
       <c r="F9" t="n">
-        <v>2.3692</v>
+        <v>0.3466</v>
       </c>
       <c r="G9" t="n">
-        <v>1.7708</v>
+        <v>5.0702</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1288</v>
+        <v>0.9999</v>
       </c>
       <c r="I9" t="n">
-        <v>1.642</v>
+        <v>4.0703</v>
       </c>
       <c r="J9" t="n">
-        <v>0.3488</v>
+        <v>3.7406</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.5328000000000001</v>
+        <v>-0.1375</v>
       </c>
       <c r="L9" t="n">
-        <v>0.8816000000000001</v>
+        <v>3.8782</v>
       </c>
       <c r="M9" t="n">
-        <v>1.422</v>
+        <v>1.3296</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6616</v>
+        <v>1.1374</v>
       </c>
       <c r="O9" t="n">
-        <v>0.7604</v>
+        <v>0.1922</v>
       </c>
       <c r="P9" t="n">
-        <v>1.1117</v>
+        <v>-1.8529</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.9264</v>
+        <v>-3.7057</v>
       </c>
       <c r="R9" t="n">
-        <v>2.0382</v>
+        <v>1.8529</v>
       </c>
       <c r="S9" t="n">
-        <v>0.3283</v>
+        <v>-0.2024</v>
       </c>
       <c r="T9" t="n">
-        <v>0.1604</v>
+        <v>-0.1986</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1679</v>
+        <v>-0.0037</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.2589</v>
+        <v>-0.6304999999999999</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>2.2016</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.2589</v>
+        <v>-2.8321</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>L. DALLACOSTA ORTIZ</t>
+          <t>J. CANDELA SOLO DE ZALDIVAR</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>1.6228</v>
+        <v>1.7561</v>
       </c>
       <c r="E10" t="n">
-        <v>1.7441</v>
+        <v>-0.613</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.1212</v>
+        <v>2.3692</v>
       </c>
       <c r="G10" t="n">
-        <v>5.0702</v>
+        <v>1.7708</v>
       </c>
       <c r="H10" t="n">
-        <v>0.9999</v>
+        <v>0.1288</v>
       </c>
       <c r="I10" t="n">
-        <v>4.0703</v>
+        <v>1.642</v>
       </c>
       <c r="J10" t="n">
-        <v>3.7406</v>
+        <v>0.3488</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.1375</v>
+        <v>-0.5328000000000001</v>
       </c>
       <c r="L10" t="n">
-        <v>3.8782</v>
+        <v>0.8816000000000001</v>
       </c>
       <c r="M10" t="n">
-        <v>1.3296</v>
+        <v>1.422</v>
       </c>
       <c r="N10" t="n">
-        <v>1.1374</v>
+        <v>0.6616</v>
       </c>
       <c r="O10" t="n">
-        <v>0.1922</v>
+        <v>0.7604</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.8529</v>
+        <v>1.1117</v>
       </c>
       <c r="Q10" t="n">
-        <v>-3.7057</v>
+        <v>-0.9264</v>
       </c>
       <c r="R10" t="n">
-        <v>1.8529</v>
+        <v>2.0382</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.964</v>
+        <v>0.1324</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4924</v>
+        <v>-0.0354</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.4716</v>
+        <v>0.1679</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.6304999999999999</v>
+        <v>-1.2589</v>
       </c>
       <c r="W10" t="n">
-        <v>2.2016</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-2.8321</v>
+        <v>-1.2589</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>F. GONZÁLEZ ROSCO</t>
+          <t>F. GONZALEZ ROSCO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,58 +1267,58 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>0.6221</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>0.6221</v>
+        <v>-2.0231</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>2.8301</v>
       </c>
       <c r="G11" t="n">
-        <v>0.6221</v>
+        <v>0.08169999999999999</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>0.1108</v>
       </c>
       <c r="I11" t="n">
-        <v>0.6221</v>
+        <v>-0.0292</v>
       </c>
       <c r="J11" t="n">
-        <v>0.6221</v>
+        <v>-1.1169</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>-0.5884</v>
       </c>
       <c r="L11" t="n">
-        <v>0.6221</v>
+        <v>-0.5284</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>1.1986</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>0.6993</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>0.4993</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-0.9264</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.4823</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>0.1694</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>0.0202</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>0.1492</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>F. GONZALEZ ROSCO</t>
+          <t>F. GONZÁLEZ ROSCO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,58 +1345,58 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>0.267</v>
+        <v>0.6221</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.3169</v>
+        <v>0.6221</v>
       </c>
       <c r="F12" t="n">
-        <v>2.5839</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>0.08169999999999999</v>
+        <v>0.6221</v>
       </c>
       <c r="H12" t="n">
-        <v>0.1108</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.0292</v>
+        <v>0.6221</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.1169</v>
+        <v>0.6221</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.5884</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.5284</v>
+        <v>0.6221</v>
       </c>
       <c r="M12" t="n">
-        <v>1.1986</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>0.6993</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>0.4993</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>0.5558999999999999</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.9264</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.4823</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.3706</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.2736</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.097</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>0.2642</v>
+        <v>0.1165</v>
       </c>
       <c r="E13" t="n">
         <v>-1.7711</v>
       </c>
       <c r="F13" t="n">
-        <v>2.0353</v>
+        <v>1.8876</v>
       </c>
       <c r="G13" t="n">
         <v>1.6158</v>
@@ -1468,13 +1468,13 @@
         <v>3.1499</v>
       </c>
       <c r="S13" t="n">
-        <v>0.4822</v>
+        <v>0.3345</v>
       </c>
       <c r="T13" t="n">
         <v>-0.0037</v>
       </c>
       <c r="U13" t="n">
-        <v>0.486</v>
+        <v>0.3382</v>
       </c>
       <c r="V13" t="n">
         <v>-2.2044</v>
@@ -1501,10 +1501,10 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>41.56990000000001</v>
+        <v>41.57010000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>17.8666</v>
+        <v>17.8669</v>
       </c>
       <c r="F14" t="n">
         <v>23.7034</v>
@@ -1522,7 +1522,7 @@
         <v>21.6647</v>
       </c>
       <c r="K14" t="n">
-        <v>8.225600000000002</v>
+        <v>8.2256</v>
       </c>
       <c r="L14" t="n">
         <v>13.4392</v>
@@ -1546,13 +1546,13 @@
         <v>22.2344</v>
       </c>
       <c r="S14" t="n">
-        <v>2.5242</v>
+        <v>2.5244</v>
       </c>
       <c r="T14" t="n">
         <v>-0.3542</v>
       </c>
       <c r="U14" t="n">
-        <v>2.8786</v>
+        <v>2.8787</v>
       </c>
       <c r="V14" t="n">
         <v>8.811500000000001</v>
@@ -1561,7 +1561,7 @@
         <v>14.1585</v>
       </c>
       <c r="X14" t="n">
-        <v>-5.347099999999999</v>
+        <v>-5.3471</v>
       </c>
     </row>
     <row r="15">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.27</v>
+        <v>-0.5392</v>
       </c>
       <c r="E16" t="n">
-        <v>0.4966</v>
+        <v>0.2028</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.7665999999999999</v>
+        <v>-0.742</v>
       </c>
       <c r="G16" t="n">
         <v>-2.0887</v>
@@ -1702,13 +1702,13 @@
         <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>0.5598</v>
+        <v>0.2907</v>
       </c>
       <c r="T16" t="n">
-        <v>0.5434</v>
+        <v>0.2496</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0164</v>
+        <v>0.041</v>
       </c>
       <c r="V16" t="n">
         <v>1.2589</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.1224</v>
+        <v>-0.9495</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.9545</v>
+        <v>-1.0524</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.168</v>
+        <v>0.1029</v>
       </c>
       <c r="G17" t="n">
         <v>-4.2423</v>
@@ -1780,13 +1780,13 @@
         <v>1.6676</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.139</v>
+        <v>0.0339</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.0584</v>
+        <v>-0.1564</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0806</v>
+        <v>0.1903</v>
       </c>
       <c r="V17" t="n">
         <v>2.5177</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. ROSA CABRERA</t>
+          <t>J. BARRIENTOS PRIETO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.3205</v>
+        <v>-1.0918</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.9591</v>
+        <v>-1.3268</v>
       </c>
       <c r="F18" t="n">
-        <v>0.6385999999999999</v>
+        <v>0.235</v>
       </c>
       <c r="G18" t="n">
-        <v>-4.0014</v>
+        <v>-0.6859</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.6389</v>
+        <v>0.1805</v>
       </c>
       <c r="I18" t="n">
-        <v>-3.3624</v>
+        <v>-0.8663999999999999</v>
       </c>
       <c r="J18" t="n">
-        <v>-2.4441</v>
+        <v>0.8479</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.6099</v>
+        <v>0.163</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.8342</v>
+        <v>0.6849</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.5573</v>
+        <v>-1.5338</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.029</v>
+        <v>0.0174</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.5283</v>
+        <v>-1.5513</v>
       </c>
       <c r="P18" t="n">
-        <v>1.6676</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-1.8529</v>
       </c>
       <c r="R18" t="n">
-        <v>1.6676</v>
+        <v>1.8529</v>
       </c>
       <c r="S18" t="n">
-        <v>0.3833</v>
+        <v>-0.7209</v>
       </c>
       <c r="T18" t="n">
-        <v>0.485</v>
+        <v>-0.6364</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1017</v>
+        <v>-0.08459999999999999</v>
       </c>
       <c r="V18" t="n">
-        <v>0.63</v>
+        <v>0.315</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>0.3144</v>
       </c>
       <c r="X18" t="n">
-        <v>0.63</v>
+        <v>0.0005</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. BARRIENTOS PRIETO</t>
+          <t>J. ROSA CABRERA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.4841</v>
+        <v>-1.6876</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.6206</v>
+        <v>-2.3508</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1365</v>
+        <v>0.6632</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.6859</v>
+        <v>-4.0014</v>
       </c>
       <c r="H19" t="n">
-        <v>0.1805</v>
+        <v>-0.6389</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.8663999999999999</v>
+        <v>-3.3624</v>
       </c>
       <c r="J19" t="n">
-        <v>0.8479</v>
+        <v>-2.4441</v>
       </c>
       <c r="K19" t="n">
-        <v>0.163</v>
+        <v>-0.6099</v>
       </c>
       <c r="L19" t="n">
-        <v>0.6849</v>
+        <v>-1.8342</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.5338</v>
+        <v>-1.5573</v>
       </c>
       <c r="N19" t="n">
-        <v>0.0174</v>
+        <v>-0.029</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.5513</v>
+        <v>-1.5283</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>1.6676</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.8529</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.8529</v>
+        <v>1.6676</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.1132</v>
+        <v>0.0162</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.9302</v>
+        <v>0.09329999999999999</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1831</v>
+        <v>-0.0771</v>
       </c>
       <c r="V19" t="n">
-        <v>0.315</v>
+        <v>0.63</v>
       </c>
       <c r="W19" t="n">
-        <v>0.3144</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0.0005</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.2674</v>
+        <v>-2.0469</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.9376</v>
+        <v>-1.7418</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3297</v>
+        <v>-0.3051</v>
       </c>
       <c r="G20" t="n">
         <v>-0.0276</v>
@@ -2014,13 +2014,13 @@
         <v>1.297</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.4424</v>
+        <v>-0.222</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.6019</v>
+        <v>-0.406</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1594</v>
+        <v>0.184</v>
       </c>
       <c r="V20" t="n">
         <v>-0.315</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. TOMAIC TOMAIC</t>
+          <t>A. CHAPARRO CARRASCO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.8976</v>
+        <v>-2.6135</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.9477</v>
+        <v>-1.1282</v>
       </c>
       <c r="F21" t="n">
-        <v>0.0502</v>
+        <v>-1.4853</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.4621</v>
+        <v>-0.8316</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.08409999999999999</v>
+        <v>-0.1787</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.378</v>
+        <v>-0.6529</v>
       </c>
       <c r="J21" t="n">
-        <v>0.8754</v>
+        <v>2.1146</v>
       </c>
       <c r="K21" t="n">
-        <v>0.8327</v>
+        <v>0.1027</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0427</v>
+        <v>2.012</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.3375</v>
+        <v>-2.9463</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.9167999999999999</v>
+        <v>-0.2814</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.4207</v>
+        <v>-2.6648</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.6676</v>
+        <v>-0.3706</v>
       </c>
       <c r="Q21" t="n">
-        <v>-4.6322</v>
+        <v>-2.7793</v>
       </c>
       <c r="R21" t="n">
-        <v>2.9646</v>
+        <v>2.4087</v>
       </c>
       <c r="S21" t="n">
-        <v>1.491</v>
+        <v>-0.7819</v>
       </c>
       <c r="T21" t="n">
-        <v>0.8096</v>
+        <v>-0.4635</v>
       </c>
       <c r="U21" t="n">
-        <v>0.6814</v>
+        <v>-0.3184</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.2589</v>
+        <v>-0.6294</v>
       </c>
       <c r="W21" t="n">
-        <v>-0.0005</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.2583</v>
+        <v>-0.6294</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. CHAPARRO CARRASCO</t>
+          <t>J. TOMAIC TOMAIC</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.2497</v>
+        <v>-3.9272</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.8137</v>
+        <v>-3.7312</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.4361</v>
+        <v>-0.196</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.8316</v>
+        <v>-1.4621</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.1787</v>
+        <v>-0.08409999999999999</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.6529</v>
+        <v>-1.378</v>
       </c>
       <c r="J22" t="n">
-        <v>2.1146</v>
+        <v>0.8754</v>
       </c>
       <c r="K22" t="n">
-        <v>0.1027</v>
+        <v>0.8327</v>
       </c>
       <c r="L22" t="n">
-        <v>2.012</v>
+        <v>0.0427</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.9463</v>
+        <v>-2.3375</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.2814</v>
+        <v>-0.9167999999999999</v>
       </c>
       <c r="O22" t="n">
-        <v>-2.6648</v>
+        <v>-1.4207</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.3706</v>
+        <v>-1.6676</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.7793</v>
+        <v>-4.6322</v>
       </c>
       <c r="R22" t="n">
-        <v>2.4087</v>
+        <v>2.9646</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.4181</v>
+        <v>0.4614</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.149</v>
+        <v>0.0261</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2691</v>
+        <v>0.4352</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.6294</v>
+        <v>-1.2589</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>-0.0005</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.6294</v>
+        <v>-1.2583</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.9459</v>
+        <v>-4.5828</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.8414</v>
+        <v>-2.429</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.1045</v>
+        <v>-2.1538</v>
       </c>
       <c r="G23" t="n">
         <v>-2.3867</v>
@@ -2248,13 +2248,13 @@
         <v>1.6676</v>
       </c>
       <c r="S23" t="n">
-        <v>0.5317</v>
+        <v>-0.1051</v>
       </c>
       <c r="T23" t="n">
-        <v>0.8133</v>
+        <v>0.2257</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.2815</v>
+        <v>-0.3308</v>
       </c>
       <c r="V23" t="n">
         <v>-2.8321</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.224</v>
+        <v>-5.1015</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.126</v>
+        <v>-3.0281</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.098</v>
+        <v>-2.0734</v>
       </c>
       <c r="G24" t="n">
         <v>-2.167</v>
@@ -2326,13 +2326,13 @@
         <v>1.297</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.6489</v>
+        <v>-0.5263</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.8207</v>
+        <v>-0.7228</v>
       </c>
       <c r="U24" t="n">
-        <v>0.1718</v>
+        <v>0.1965</v>
       </c>
       <c r="V24" t="n">
         <v>0.0005</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-5.2339</v>
+        <v>-5.1863</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.5479</v>
+        <v>-2.2541</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.686</v>
+        <v>-2.9322</v>
       </c>
       <c r="G25" t="n">
         <v>-3.1404</v>
@@ -2404,13 +2404,13 @@
         <v>0.5558999999999999</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.1306</v>
+        <v>-0.083</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.6566</v>
+        <v>-0.3628</v>
       </c>
       <c r="U25" t="n">
-        <v>0.526</v>
+        <v>0.2798</v>
       </c>
       <c r="V25" t="n">
         <v>-2.5188</v>
@@ -2437,10 +2437,10 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-5.7228</v>
+        <v>-5.429</v>
       </c>
       <c r="E26" t="n">
-        <v>-1.4884</v>
+        <v>-1.1946</v>
       </c>
       <c r="F26" t="n">
         <v>-4.2344</v>
@@ -2482,10 +2482,10 @@
         <v>1.1117</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.7411</v>
+        <v>-0.4474</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.766</v>
+        <v>-0.4722</v>
       </c>
       <c r="U26" t="n">
         <v>0.0249</v>
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-9.7758</v>
+        <v>-9.3589</v>
       </c>
       <c r="E27" t="n">
-        <v>-4.907</v>
+        <v>-4.6133</v>
       </c>
       <c r="F27" t="n">
-        <v>-4.8687</v>
+        <v>-4.7456</v>
       </c>
       <c r="G27" t="n">
         <v>-3.1424</v>
@@ -2560,13 +2560,13 @@
         <v>1.1117</v>
       </c>
       <c r="S27" t="n">
-        <v>-0.8568</v>
+        <v>-0.4399</v>
       </c>
       <c r="T27" t="n">
-        <v>-0.5471</v>
+        <v>-0.2534</v>
       </c>
       <c r="U27" t="n">
-        <v>-0.3096</v>
+        <v>-0.1865</v>
       </c>
       <c r="V27" t="n">
         <v>-5.0354</v>
@@ -2593,10 +2593,10 @@
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>-41.56999999999999</v>
+        <v>-41.5701</v>
       </c>
       <c r="E28" t="n">
-        <v>-23.7032</v>
+        <v>-23.7034</v>
       </c>
       <c r="F28" t="n">
         <v>-17.8667</v>
@@ -2611,7 +2611,7 @@
         <v>-15.4758</v>
       </c>
       <c r="J28" t="n">
-        <v>-3.937500000000001</v>
+        <v>-3.9375</v>
       </c>
       <c r="K28" t="n">
         <v>-1.9009</v>
@@ -2632,7 +2632,7 @@
         <v>-4.6322</v>
       </c>
       <c r="Q28" t="n">
-        <v>-22.2344</v>
+        <v>-22.23439999999999</v>
       </c>
       <c r="R28" t="n">
         <v>17.6023</v>
@@ -2641,7 +2641,7 @@
         <v>-2.5243</v>
       </c>
       <c r="T28" t="n">
-        <v>-2.8786</v>
+        <v>-2.8788</v>
       </c>
       <c r="U28" t="n">
         <v>0.3543000000000001</v>
